--- a/Action/Data/CSV/Platform1/PlatformId.xlsx
+++ b/Action/Data/CSV/Platform1/PlatformId.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ita20\OneDrive\デスクトップ\GameProject\Action\Data\CSV\Platform\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ita20\OneDrive\デスクトップ\Action - コピー\Data\CSV\Platform1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{82FFD05A-E3F8-4131-A6E2-2611128AE55C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{743365F2-E29D-45F0-9C98-ECB50D4D41D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="11295" xr2:uid="{A378E325-DACB-423B-896D-A4D927572F7E}"/>
+    <workbookView xWindow="6840" yWindow="4185" windowWidth="21600" windowHeight="11295" xr2:uid="{A378E325-DACB-423B-896D-A4D927572F7E}"/>
   </bookViews>
   <sheets>
     <sheet name="PlatformId" sheetId="1" r:id="rId1"/>
@@ -732,22 +732,22 @@
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A68">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A69">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A70">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A71">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.4">

--- a/Action/Data/CSV/Platform1/PlatformId.xlsx
+++ b/Action/Data/CSV/Platform1/PlatformId.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ita20\OneDrive\デスクトップ\Action - コピー\Data\CSV\Platform1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2409404\Desktop\GameProject\Action\Data\CSV\Platform1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{743365F2-E29D-45F0-9C98-ECB50D4D41D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0393844C-3036-4F39-83D3-04C4D38F7853}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6840" yWindow="4185" windowWidth="21600" windowHeight="11295" xr2:uid="{A378E325-DACB-423B-896D-A4D927572F7E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A378E325-DACB-423B-896D-A4D927572F7E}"/>
   </bookViews>
   <sheets>
     <sheet name="PlatformId" sheetId="1" r:id="rId1"/>
@@ -96,9 +96,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -136,7 +136,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -242,7 +242,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -384,7 +384,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -392,7 +392,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BFD7BC8-9980-4F3F-8CC7-03B88A271EE4}">
-  <dimension ref="A1:A100"/>
+  <dimension ref="A1:A99"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
@@ -717,37 +717,37 @@
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A65">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A66">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A67">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A68">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A69">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A70">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A71">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.4">
@@ -887,11 +887,6 @@
     </row>
     <row r="99" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A99">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A100">
         <v>0</v>
       </c>
     </row>

--- a/Action/Data/CSV/Platform1/PlatformId.xlsx
+++ b/Action/Data/CSV/Platform1/PlatformId.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2409404\Desktop\GameProject\Action\Data\CSV\Platform1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0393844C-3036-4F39-83D3-04C4D38F7853}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{13613A52-54FE-4F71-A179-189889FCB0D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A378E325-DACB-423B-896D-A4D927572F7E}"/>
+    <workbookView xWindow="1560" yWindow="6195" windowWidth="21600" windowHeight="11295" xr2:uid="{A378E325-DACB-423B-896D-A4D927572F7E}"/>
   </bookViews>
   <sheets>
     <sheet name="PlatformId" sheetId="1" r:id="rId1"/>
@@ -727,17 +727,17 @@
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A67">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A68">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A69">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.4">

--- a/Action/Data/CSV/Platform1/PlatformId.xlsx
+++ b/Action/Data/CSV/Platform1/PlatformId.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2409404\Desktop\GameProject\Action\Data\CSV\Platform1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{13613A52-54FE-4F71-A179-189889FCB0D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D4A3CFFB-9759-4506-AAB7-8E56B87D67AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="6195" windowWidth="21600" windowHeight="11295" xr2:uid="{A378E325-DACB-423B-896D-A4D927572F7E}"/>
+    <workbookView xWindow="5610" yWindow="4185" windowWidth="21600" windowHeight="11295" xr2:uid="{A378E325-DACB-423B-896D-A4D927572F7E}"/>
   </bookViews>
   <sheets>
     <sheet name="PlatformId" sheetId="1" r:id="rId1"/>
@@ -392,7 +392,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BFD7BC8-9980-4F3F-8CC7-03B88A271EE4}">
-  <dimension ref="A1:A99"/>
+  <dimension ref="A1:A100"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
@@ -742,17 +742,17 @@
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A70">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A71">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A72">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.4">
@@ -887,6 +887,11 @@
     </row>
     <row r="99" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A100">
         <v>0</v>
       </c>
     </row>

--- a/Action/Data/CSV/Platform1/PlatformId.xlsx
+++ b/Action/Data/CSV/Platform1/PlatformId.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2409404\Desktop\GameProject\Action\Data\CSV\Platform1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D4A3CFFB-9759-4506-AAB7-8E56B87D67AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F4CB1A4C-6E54-4725-920D-5F966AE482D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5610" yWindow="4185" windowWidth="21600" windowHeight="11295" xr2:uid="{A378E325-DACB-423B-896D-A4D927572F7E}"/>
   </bookViews>
@@ -717,12 +717,12 @@
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A65">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A66">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.4">
@@ -757,12 +757,12 @@
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A73">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A74">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.4">

--- a/Action/Data/CSV/Platform1/PlatformId.xlsx
+++ b/Action/Data/CSV/Platform1/PlatformId.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2409404\Desktop\GameProject\Action\Data\CSV\Platform1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ita20\OneDrive\デスクトップ\GameProject\Action\Data\CSV\Platform1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F4CB1A4C-6E54-4725-920D-5F966AE482D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{01369B5A-FFDB-4A4C-9B1F-27F7976FD4E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5610" yWindow="4185" windowWidth="21600" windowHeight="11295" xr2:uid="{A378E325-DACB-423B-896D-A4D927572F7E}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{A378E325-DACB-423B-896D-A4D927572F7E}"/>
   </bookViews>
   <sheets>
     <sheet name="PlatformId" sheetId="1" r:id="rId1"/>
@@ -96,9 +96,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 テーマ">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -136,7 +136,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -242,7 +242,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -384,7 +384,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -392,7 +392,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BFD7BC8-9980-4F3F-8CC7-03B88A271EE4}">
-  <dimension ref="A1:A100"/>
+  <dimension ref="A1:A92"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
@@ -682,87 +682,87 @@
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A58">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A59">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A60">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A61">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A62">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A63">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A64">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A65">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A66">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A67">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A68">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A69">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A70">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A71">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A72">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A73">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A74">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.4">
@@ -852,46 +852,6 @@
     </row>
     <row r="92" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A92">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A93">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A94">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A95">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A96">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A97">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A98">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A99">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A100">
         <v>0</v>
       </c>
     </row>
